--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,22 +98,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -517,6 +526,24 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -528,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -540,35 +567,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Armaturer</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Armaturer</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>LED-Panel</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Övrigt</t>
-        </is>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -591,1173 +636,1173 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Produktnamn</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>7476990</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>7476991</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>7476994</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>7476995</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>7476992</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7476993</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>7476996</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>7476997</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>7577717</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Plafond CCL-01</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>7577718</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Plafond CCL-01</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>7577719</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Plafond CCL-01-S</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>7577720</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Plafond CCL-01-S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>7706311</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT 1</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>7706312</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT 1</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>7706313</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT 1</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>7706614</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>7706615</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>7706616</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>7706621</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02-U, med eluttag</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>7706622</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02-U, med eluttag</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>7706623</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02-U, med eluttag</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>1377749</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Dimmer DALI bcast 128mA DT8 BT</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>1377701</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Dosdimmer 300VA LED mesh BT</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>1377703</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Krondimmer 2x100VA LED mesh BT</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>1377742</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Smart plug dimmer</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>7077777</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Infälld armatur LED-panel LPN-01</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>LED-Panel</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>8581183</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>8581182</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>8581181</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>8581284</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>8581285</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>8581286</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>7077725</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Anslutningskabel CTN-01</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>1377732</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Batteribackup för klocka</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>1377702</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Controller 0/1-10V 16A mesh BT</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>7984810</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Driver LED Bluetooth</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>1377767</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Extender 2xin bat mesh BT</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>1377705</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Gateway Bluetooth Internet</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>1893378</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Knappingång trådlös</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>7077726</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Kopplingsbox CTN-02</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>1377706</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Kronrelä 16A/2 mesh Bluetooth</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>7984895</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>LED Driver,12/24VDC Tunable White</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>7509808E</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>LEDstrip LST01</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>7509809</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>LEDstrip LST01</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>7509810</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>LEDstrip LST01</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>1377790</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Monteringsclips DIN/vägg</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>1377791</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Monteringsdosa</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>1377709</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Relä 2-pol 16A/13A mesh Bluetooth</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>1307779</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Rörelsevakt trådlös hörnmonterad</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>1377740</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>1377741</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>1893380</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Styrenhet för jalusier</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>1377722</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>1377723</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>1377721</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>1377724</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>1377708</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>1377726</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>1377773</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>1377772</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>1377707</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>1377727</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>1377737</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>1377735</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>1377733</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>1377734</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>1377736</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>1377738</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -107,6 +107,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -544,6 +547,25 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>320</v>
+      </c>
+      <c r="C3" t="n">
+        <v>130</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>284</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -555,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -567,32 +589,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Armaturer</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Armaturer</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>LED-Panel</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
@@ -614,6 +636,28 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" t="n">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -636,1173 +680,1173 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Produktnamn</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>7476990</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>7476991</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>7476994</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>7476995</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-01 tiltbar</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>7476992</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7476993</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>7476996</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>7476997</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Downlight DWN-02</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>7577717</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Plafond CCL-01</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>7577718</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Plafond CCL-01</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>7577719</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Plafond CCL-01-S</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>7577720</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Plafond CCL-01-S</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>7706311</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT 1</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>7706312</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT 1</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>7706313</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT 1</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>7706614</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>7706615</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>7706616</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>7706621</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02-U, med eluttag</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>7706622</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02-U, med eluttag</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>7706623</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Väggarmatur OUT-02-U, med eluttag</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Armaturer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>1377749</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Dimmer DALI bcast 128mA DT8 BT</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>1377701</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Dosdimmer 300VA LED mesh BT</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>1377703</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Krondimmer 2x100VA LED mesh BT</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>1377742</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Smart plug dimmer</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Dimmer</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>7077777</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Infälld armatur LED-panel LPN-01</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>LED-Panel</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>8581183</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>8581182</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>8581181</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>8581284</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>8581285</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>8581286</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>7077725</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Anslutningskabel CTN-01</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>1377732</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Batteribackup för klocka</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>1377702</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Controller 0/1-10V 16A mesh BT</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>7984810</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Driver LED Bluetooth</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>1377767</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Extender 2xin bat mesh BT</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>1377705</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Gateway Bluetooth Internet</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>1893378</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Knappingång trådlös</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>7077726</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Kopplingsbox CTN-02</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>1377706</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Kronrelä 16A/2 mesh Bluetooth</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>7984895</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>LED Driver,12/24VDC Tunable White</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>7509808E</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>LEDstrip LST01</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>7509809</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>LEDstrip LST01</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>7509810</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>LEDstrip LST01</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>1377790</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Monteringsclips DIN/vägg</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>1377791</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>Monteringsdosa</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>1377709</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Relä 2-pol 16A/13A mesh Bluetooth</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>1307779</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>Rörelsevakt trådlös hörnmonterad</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>1377740</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>1377741</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>1893380</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Styrenhet för jalusier</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>1377722</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>1377723</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>1377721</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>1377724</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>1377708</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>1377726</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>1377773</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>1377772</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>1377707</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>1377727</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>1377737</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>1377735</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>1377733</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>1377734</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>1377736</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>1377738</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -566,6 +566,28 @@
         <v>284</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -577,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -658,6 +680,28 @@
       </c>
       <c r="F3" t="n">
         <v>267</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -588,6 +588,16 @@
         <v>231</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -599,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -702,6 +712,13 @@
       </c>
       <c r="F4" s="3" t="n">
         <v>282</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -598,6 +598,18 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -609,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -720,6 +732,18 @@
           <t>2026-05-31</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -610,6 +610,28 @@
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>305</v>
+      </c>
+      <c r="C7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -621,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -744,6 +766,28 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>476</v>
+      </c>
+      <c r="C7" t="n">
+        <v>154</v>
+      </c>
+      <c r="D7" t="n">
+        <v>104</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>331</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -632,6 +632,28 @@
         <v>282</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -643,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -787,6 +809,28 @@
       </c>
       <c r="F7" t="n">
         <v>331</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -654,6 +654,28 @@
         <v>316</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" t="n">
+        <v>114</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -665,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -831,6 +853,28 @@
       </c>
       <c r="F8" s="3" t="n">
         <v>242</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>304</v>
+      </c>
+      <c r="C9" t="n">
+        <v>81</v>
+      </c>
+      <c r="D9" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -676,6 +676,28 @@
         <v>273</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -687,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -875,6 +897,28 @@
       </c>
       <c r="F9" t="n">
         <v>295</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -698,6 +698,28 @@
         <v>222</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>211</v>
+      </c>
+      <c r="C11" t="n">
+        <v>87</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -709,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -919,6 +941,25 @@
       </c>
       <c r="F10" s="3" t="n">
         <v>328</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>374</v>
+      </c>
+      <c r="C11" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -720,6 +720,18 @@
         <v>233</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -731,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -961,6 +973,18 @@
       <c r="F11" t="n">
         <v>414</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -732,6 +732,13 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -743,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -985,6 +992,13 @@
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -739,6 +739,28 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -750,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -998,6 +1020,26 @@
         <is>
           <t>2026-06-08</t>
         </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>508</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,28 @@
         <v>282</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>268</v>
+      </c>
+      <c r="C15" t="n">
+        <v>114</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -772,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1040,6 +1062,25 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n">
         <v>363</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>398</v>
+      </c>
+      <c r="C15" t="n">
+        <v>167</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34</v>
+      </c>
+      <c r="F15" t="n">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -783,6 +783,26 @@
         <v>316</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>274</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -794,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1101,26 @@
       </c>
       <c r="F15" t="n">
         <v>335</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -803,6 +803,25 @@
         <v>274</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>276</v>
+      </c>
+      <c r="C17" t="n">
+        <v>96</v>
+      </c>
+      <c r="D17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>226</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -814,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1140,25 @@
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n">
         <v>167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>239</v>
+      </c>
+      <c r="C17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -822,6 +822,28 @@
         <v>226</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -833,7 +855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1159,6 +1181,26 @@
       </c>
       <c r="F17" t="n">
         <v>385</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -844,6 +844,16 @@
         <v>279</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -855,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1201,6 +1211,13 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n">
         <v>126</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -854,6 +854,26 @@
         <v>7</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -865,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1219,6 +1239,18 @@
           <t>2026-06-14</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -874,6 +874,25 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>339</v>
+      </c>
+      <c r="C21" t="n">
+        <v>124</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="F21" t="n">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -885,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1270,25 @@
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>408</v>
+      </c>
+      <c r="C21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" t="n">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -893,6 +893,26 @@
         <v>292</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -904,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1288,6 +1308,28 @@
       </c>
       <c r="F21" t="n">
         <v>231</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -913,6 +913,28 @@
         <v>290</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>312</v>
+      </c>
+      <c r="C23" t="n">
+        <v>123</v>
+      </c>
+      <c r="D23" t="n">
+        <v>21</v>
+      </c>
+      <c r="E23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -924,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1330,6 +1352,28 @@
       </c>
       <c r="F22" s="3" t="n">
         <v>318</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>127</v>
+      </c>
+      <c r="C23" t="n">
+        <v>89</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -935,6 +935,28 @@
         <v>315</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -946,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1374,6 +1396,26 @@
       </c>
       <c r="F23" t="n">
         <v>196</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>466</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n">
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -957,6 +957,13 @@
         <v>254</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -968,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1416,6 +1423,13 @@
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n">
         <v>486</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -964,6 +964,20 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -975,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1445,18 @@
           <t>2026-06-20</t>
         </is>
       </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -978,6 +978,13 @@
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -989,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1457,6 +1464,13 @@
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -985,6 +985,28 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -996,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1470,6 +1492,26 @@
         <is>
           <t>2026-06-22</t>
         </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1007,28 @@
         <v>260</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>321</v>
+      </c>
+      <c r="C29" t="n">
+        <v>109</v>
+      </c>
+      <c r="D29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1018,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1512,6 +1534,28 @@
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n">
         <v>172</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>127</v>
+      </c>
+      <c r="C29" t="n">
+        <v>66</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1029,6 +1029,28 @@
         <v>270</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1040,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1556,6 +1578,26 @@
       </c>
       <c r="F29" t="n">
         <v>131</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1051,6 +1051,28 @@
         <v>261</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>264</v>
+      </c>
+      <c r="C31" t="n">
+        <v>122</v>
+      </c>
+      <c r="D31" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1062,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1598,6 +1620,28 @@
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n">
         <v>182</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>286</v>
+      </c>
+      <c r="C31" t="n">
+        <v>113</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,28 @@
         <v>259</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1084,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1642,6 +1664,26 @@
       </c>
       <c r="F31" t="n">
         <v>177</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1095,6 +1095,13 @@
         <v>233</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1106,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1684,6 +1691,13 @@
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n">
         <v>198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1102,20 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1113,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1699,6 +1713,18 @@
           <t>2026-06-28</t>
         </is>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1116,6 +1116,28 @@
         <v>3</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>235</v>
+      </c>
+      <c r="C35" t="n">
+        <v>136</v>
+      </c>
+      <c r="D35" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18</v>
+      </c>
+      <c r="F35" t="n">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1127,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1726,6 +1748,28 @@
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>138</v>
+      </c>
+      <c r="C35" t="n">
+        <v>42</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1737,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2188,65 +2232,65 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>1377715</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-L</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Dimmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>1377716</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-L</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Dimmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>7077777</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Infälld armatur LED-panel LPN-01</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>LED-Panel</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>8581183</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Termostat TRM-01</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Termostat</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>8581182</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Termostat TRM-01</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Termostat</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>8581181</t>
+          <t>8581287</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Termostat TRM-01</t>
+          <t>Golvvärmetermostat TRM-01-L</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2258,12 +2302,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>8581284</t>
+          <t>8581288</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Termostat TRM-01</t>
+          <t>Golvvärmetermostat TRM-01-L</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2275,7 +2319,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>8581285</t>
+          <t>8581183</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -2292,97 +2336,97 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>8581182</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Termostat TRM-01</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Termostat</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>8581181</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Termostat TRM-01</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Termostat</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>8581284</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Termostat TRM-01</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Termostat</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>8581285</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Termostat TRM-01</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Termostat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
           <t>8581286</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Termostat TRM-01</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Termostat</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>7077725</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Anslutningskabel CTN-01</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Övrigt</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>1377732</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Batteribackup för klocka</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Övrigt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>1377702</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Controller 0/1-10V 16A mesh BT</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Övrigt</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>7984810</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Driver LED Bluetooth</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Övrigt</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>1377767</t>
+          <t>7077725</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Extender 2xin bat mesh BT</t>
+          <t>Anslutningskabel CTN-01</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -2394,12 +2438,12 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>1377705</t>
+          <t>1377732</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Gateway Bluetooth Internet</t>
+          <t>Batteribackup för klocka</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -2411,12 +2455,12 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>1893378</t>
+          <t>1377702</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Knappingång trådlös</t>
+          <t>Controller 0/1-10V 16A mesh BT</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -2428,12 +2472,12 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>7077726</t>
+          <t>7984810</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Kopplingsbox CTN-02</t>
+          <t>Driver LED Bluetooth</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -2445,12 +2489,12 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>1377706</t>
+          <t>1377767</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Kronrelä 16A/2 mesh Bluetooth</t>
+          <t>Extender 2xin bat mesh BT</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -2462,12 +2506,12 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>7984895</t>
+          <t>1377705</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>LED Driver,12/24VDC Tunable White</t>
+          <t>Gateway Bluetooth Internet</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -2479,12 +2523,12 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>7509808E</t>
+          <t>1893378</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>LEDstrip LST01</t>
+          <t>Knappingång trådlös</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -2496,12 +2540,12 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>7509809</t>
+          <t>7077726</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>LEDstrip LST01</t>
+          <t>Kopplingsbox CTN-02</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -2513,12 +2557,12 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>7509810</t>
+          <t>1377706</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>LEDstrip LST01</t>
+          <t>Kronrelä 16A/2 mesh Bluetooth</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -2530,12 +2574,12 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>1377790</t>
+          <t>7984895</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Monteringsclips DIN/vägg</t>
+          <t>LED Driver,12/24VDC Tunable White</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -2547,12 +2591,12 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>1377791</t>
+          <t>7509808E</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Monteringsdosa</t>
+          <t>LEDstrip LST01</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -2564,12 +2608,12 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>1377709</t>
+          <t>7509809</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Relä 2-pol 16A/13A mesh Bluetooth</t>
+          <t>LEDstrip LST01</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -2581,12 +2625,12 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>1307779</t>
+          <t>7509810</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Rörelsevakt trådlös hörnmonterad</t>
+          <t>LEDstrip LST01</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -2598,12 +2642,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1377740</t>
+          <t>1377790</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
+          <t>Monteringsclips DIN/vägg</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -2615,12 +2659,12 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1377741</t>
+          <t>1377791</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
+          <t>Monteringsdosa</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -2632,12 +2676,12 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1893380</t>
+          <t>1377709</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Styrenhet för jalusier</t>
+          <t>Relä 2-pol 16A/13A mesh Bluetooth</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -2649,12 +2693,12 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1377722</t>
+          <t>1307779</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-E</t>
+          <t>Rörelsevakt trådlös hörnmonterad</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -2666,12 +2710,12 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1377723</t>
+          <t>1377740</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-E</t>
+          <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -2683,12 +2727,12 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1377721</t>
+          <t>1377741</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-S</t>
+          <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -2700,12 +2744,12 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1377724</t>
+          <t>1893380</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-S</t>
+          <t>Styrenhet för jalusier</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -2717,12 +2761,12 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1377708</t>
+          <t>1377722</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -2734,12 +2778,12 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1377726</t>
+          <t>1377723</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -2751,12 +2795,12 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1377773</t>
+          <t>1377721</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -2768,12 +2812,12 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1377772</t>
+          <t>1377724</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -2785,12 +2829,12 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1377707</t>
+          <t>1377708</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -2802,12 +2846,12 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1377727</t>
+          <t>1377726</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -2819,12 +2863,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1377737</t>
+          <t>1377713</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -2836,12 +2880,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1377735</t>
+          <t>1377714</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -2853,12 +2897,12 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1377733</t>
+          <t>1377773</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -2870,12 +2914,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1377734</t>
+          <t>1377772</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -2887,12 +2931,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1377736</t>
+          <t>1377707</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+          <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -2904,15 +2948,117 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
+          <t>1377727</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Trådlös vridratt WRT-01-S</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>1377737</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>1377735</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>1377733</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>1377734</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>1377736</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
           <t>1377738</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1138,6 +1138,28 @@
         <v>275</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1149,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1768,6 +1790,28 @@
       </c>
       <c r="F35" t="n">
         <v>178</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1160,6 +1160,28 @@
         <v>297</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>260</v>
+      </c>
+      <c r="C37" t="n">
+        <v>105</v>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1171,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1812,6 +1834,28 @@
       </c>
       <c r="F36" s="3" t="n">
         <v>254</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>210</v>
+      </c>
+      <c r="C37" t="n">
+        <v>190</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1182,6 +1182,28 @@
         <v>242</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>286</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1193,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1856,6 +1878,28 @@
       </c>
       <c r="F37" t="n">
         <v>352</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1204,6 +1204,25 @@
         <v>286</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>168</v>
+      </c>
+      <c r="C39" t="n">
+        <v>98</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="F39" t="n">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1215,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1900,6 +1919,28 @@
       </c>
       <c r="F38" s="3" t="n">
         <v>315</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>266</v>
+      </c>
+      <c r="C39" t="n">
+        <v>126</v>
+      </c>
+      <c r="D39" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1223,6 +1223,18 @@
         <v>190</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1234,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1942,6 +1954,18 @@
       <c r="F39" t="n">
         <v>135</v>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1235,6 +1235,13 @@
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1246,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1966,6 +1973,13 @@
       <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1242,6 +1242,28 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1253,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1979,6 +2001,26 @@
         <is>
           <t>2026-07-06</t>
         </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>578</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1264,6 +1264,28 @@
         <v>231</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>228</v>
+      </c>
+      <c r="C43" t="n">
+        <v>97</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1275,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2021,6 +2043,25 @@
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n">
         <v>252</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>56</v>
+      </c>
+      <c r="C43" t="n">
+        <v>42</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1286,6 +1286,28 @@
         <v>258</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1297,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2084,26 @@
       </c>
       <c r="F43" t="n">
         <v>71</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1308,6 +1308,28 @@
         <v>206</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>218</v>
+      </c>
+      <c r="C45" t="n">
+        <v>77</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1319,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2104,6 +2126,25 @@
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
         <v>149</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>36</v>
+      </c>
+      <c r="C45" t="n">
+        <v>115</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1330,6 +1330,28 @@
         <v>167</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1341,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2167,28 @@
       </c>
       <c r="F45" t="n">
         <v>201</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1352,6 +1352,22 @@
         <v>129</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1363,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2189,6 +2205,13 @@
       </c>
       <c r="F46" s="3" t="n">
         <v>313</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1368,6 +1368,18 @@
         <v>1</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1379,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2225,18 @@
           <t>2026-07-12</t>
         </is>
       </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1380,6 +1380,25 @@
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>121</v>
+      </c>
+      <c r="C49" t="n">
+        <v>71</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1391,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2256,28 @@
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>284</v>
+      </c>
+      <c r="C49" t="n">
+        <v>37</v>
+      </c>
+      <c r="D49" t="n">
+        <v>23</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>468</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1399,6 +1399,26 @@
         <v>129</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1410,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2277,6 +2297,28 @@
       </c>
       <c r="F49" t="n">
         <v>468</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1419,6 +1419,22 @@
         <v>102</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>137</v>
+      </c>
+      <c r="C51" t="n">
+        <v>61</v>
+      </c>
+      <c r="F51" t="n">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1430,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2319,6 +2335,25 @@
       </c>
       <c r="F50" s="3" t="n">
         <v>73</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>59</v>
+      </c>
+      <c r="C51" t="n">
+        <v>150</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1435,6 +1435,26 @@
         <v>132</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1446,7 +1466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2354,6 +2374,26 @@
       </c>
       <c r="F51" t="n">
         <v>189</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1455,6 +1455,25 @@
         <v>131</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>115</v>
+      </c>
+      <c r="C53" t="n">
+        <v>31</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1466,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2394,6 +2413,28 @@
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n">
         <v>140</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>186</v>
+      </c>
+      <c r="C53" t="n">
+        <v>52</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1474,6 +1474,18 @@
         <v>122</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1485,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2436,6 +2448,18 @@
       <c r="F53" t="n">
         <v>71</v>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1486,6 +1486,13 @@
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1497,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2460,6 +2467,13 @@
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1493,6 +1493,26 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1504,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2473,6 +2493,26 @@
         <is>
           <t>2026-07-20</t>
         </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1513,6 +1513,25 @@
         <v>155</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>115</v>
+      </c>
+      <c r="C57" t="n">
+        <v>60</v>
+      </c>
+      <c r="D57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="n">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2513,6 +2532,25 @@
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n">
         <v>186</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>71</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" t="n">
+        <v>27</v>
+      </c>
+      <c r="F57" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1532,6 +1532,28 @@
         <v>127</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1543,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2551,6 +2573,26 @@
       </c>
       <c r="F57" t="n">
         <v>109</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1554,6 +1554,28 @@
         <v>123</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>92</v>
+      </c>
+      <c r="C59" t="n">
+        <v>58</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1565,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2593,6 +2615,25 @@
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n">
         <v>151</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>85</v>
+      </c>
+      <c r="C59" t="n">
+        <v>42</v>
+      </c>
+      <c r="D59" t="n">
+        <v>14</v>
+      </c>
+      <c r="F59" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1576,6 +1576,26 @@
         <v>105</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1587,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2634,6 +2654,26 @@
       </c>
       <c r="F59" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1596,6 +1596,16 @@
         <v>115</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1607,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2674,6 +2684,13 @@
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n">
         <v>139</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1606,6 +1606,18 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1617,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2692,6 +2704,18 @@
           <t>2026-07-26</t>
         </is>
       </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1618,6 +1618,25 @@
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
     </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>191</v>
+      </c>
+      <c r="C63" t="n">
+        <v>75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1629,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2716,6 +2735,25 @@
       <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>94</v>
+      </c>
+      <c r="C63" t="n">
+        <v>61</v>
+      </c>
+      <c r="D63" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1637,6 +1637,26 @@
         <v>123</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1648,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2753,6 +2773,26 @@
       </c>
       <c r="F63" t="n">
         <v>127</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1657,6 +1657,25 @@
         <v>137</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>107</v>
+      </c>
+      <c r="C65" t="n">
+        <v>36</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1668,7 +1687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2793,6 +2812,25 @@
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n">
         <v>118</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" t="n">
+        <v>32</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1676,6 +1676,26 @@
         <v>110</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1687,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2831,6 +2851,26 @@
       </c>
       <c r="F65" t="n">
         <v>275</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1696,6 +1696,25 @@
         <v>127</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>127</v>
+      </c>
+      <c r="C67" t="n">
+        <v>28</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1707,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2871,6 +2890,25 @@
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n">
         <v>173</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>111</v>
+      </c>
+      <c r="C67" t="n">
+        <v>67</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1715,6 +1715,20 @@
         <v>98</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n">
+        <v>1402</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1726,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2910,6 +2924,18 @@
       <c r="F67" t="n">
         <v>85</v>
       </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1729,6 +1729,22 @@
         <v>1402</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1740,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2936,6 +2952,16 @@
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1401</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1745,6 +1745,28 @@
         <v>3</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1756,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2961,6 +2983,26 @@
       </c>
       <c r="F69" t="n">
         <v>1401</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1767,6 +1767,25 @@
         <v>183</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>192</v>
+      </c>
+      <c r="C71" t="n">
+        <v>47</v>
+      </c>
+      <c r="D71" t="n">
+        <v>9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1778,7 +1797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3003,6 +3022,25 @@
       </c>
       <c r="F70" s="3" t="n">
         <v>152</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>119</v>
+      </c>
+      <c r="C71" t="n">
+        <v>11</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1786,6 +1786,26 @@
         <v>220</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1797,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3041,6 +3061,28 @@
       </c>
       <c r="F71" t="n">
         <v>113</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1806,6 +1806,25 @@
         <v>171</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>275</v>
+      </c>
+      <c r="C73" t="n">
+        <v>128</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>626</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1817,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3083,6 +3102,28 @@
       </c>
       <c r="F72" s="3" t="n">
         <v>107</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>135</v>
+      </c>
+      <c r="C73" t="n">
+        <v>73</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" t="n">
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1825,6 +1825,28 @@
         <v>626</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>479</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1836,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3126,6 +3148,24 @@
         <v>270</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>418</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3137,7 +3177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4151,12 +4191,12 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1377721</t>
+          <t>1377711</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-S</t>
+          <t>Tryckknapp trådlös WPH-01-L</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -4168,12 +4208,12 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1377724</t>
+          <t>1377712</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-S</t>
+          <t>Tryckknapp trådlös WPH-01-L</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -4185,12 +4225,12 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1377708</t>
+          <t>1377721</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -4202,12 +4242,12 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1377726</t>
+          <t>1377724</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -4219,12 +4259,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1377713</t>
+          <t>1377708</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-L</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -4236,12 +4276,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1377714</t>
+          <t>1377726</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-L</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -4253,12 +4293,12 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1377773</t>
+          <t>1377713</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -4270,12 +4310,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1377772</t>
+          <t>1377714</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -4287,12 +4327,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1377707</t>
+          <t>1377773</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -4304,12 +4344,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1377727</t>
+          <t>1377772</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -4321,12 +4361,12 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1377737</t>
+          <t>1377707</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -4338,12 +4378,12 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1377735</t>
+          <t>1377727</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -4355,12 +4395,12 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1377733</t>
+          <t>1377737</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -4372,12 +4412,12 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1377734</t>
+          <t>1377735</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -4389,12 +4429,12 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1377736</t>
+          <t>1377733</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -4406,15 +4446,49 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
+          <t>1377734</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>1377736</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
           <t>1377738</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1847,6 +1847,16 @@
         <v>479</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1858,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3164,6 +3174,13 @@
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n">
         <v>168</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1857,6 +1857,20 @@
         <v>3</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1868,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3182,6 +3196,18 @@
           <t>2026-08-09</t>
         </is>
       </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1871,6 +1871,25 @@
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
     </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>232</v>
+      </c>
+      <c r="C77" t="n">
+        <v>121</v>
+      </c>
+      <c r="D77" t="n">
+        <v>17</v>
+      </c>
+      <c r="F77" t="n">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1882,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3208,6 +3227,25 @@
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>178</v>
+      </c>
+      <c r="C77" t="n">
+        <v>70</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>214</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1890,6 +1890,28 @@
         <v>205</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1901,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3245,6 +3267,26 @@
       </c>
       <c r="F77" t="n">
         <v>214</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1912,6 +1912,25 @@
         <v>255</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>314</v>
+      </c>
+      <c r="C79" t="n">
+        <v>75</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22</v>
+      </c>
+      <c r="F79" t="n">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1923,7 +1942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3287,6 +3306,28 @@
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n">
         <v>260</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>153</v>
+      </c>
+      <c r="C79" t="n">
+        <v>78</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1931,6 +1931,28 @@
         <v>257</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1942,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3328,6 +3350,26 @@
       </c>
       <c r="F79" t="n">
         <v>233</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n">
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1953,6 +1953,28 @@
         <v>265</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>199</v>
+      </c>
+      <c r="C81" t="n">
+        <v>55</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16</v>
+      </c>
+      <c r="E81" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" t="n">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1964,7 +1986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3370,6 +3392,28 @@
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n">
         <v>232</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>268</v>
+      </c>
+      <c r="C81" t="n">
+        <v>86</v>
+      </c>
+      <c r="D81" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" t="n">
+        <v>12</v>
+      </c>
+      <c r="F81" t="n">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1975,6 +1975,22 @@
         <v>193</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1986,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3415,6 +3431,18 @@
       <c r="F81" t="n">
         <v>285</v>
       </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1991,6 +1991,16 @@
         <v>3</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2002,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3443,6 +3453,13 @@
       <c r="D82" s="3" t="n"/>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2001,6 +2001,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>359</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2012,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3459,6 +3481,28 @@
         <is>
           <t>2026-08-17</t>
         </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2023,6 +2023,28 @@
         <v>359</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>312</v>
+      </c>
+      <c r="C85" t="n">
+        <v>82</v>
+      </c>
+      <c r="D85" t="n">
+        <v>16</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2034,7 +2056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3503,6 +3525,28 @@
       </c>
       <c r="F84" s="3" t="n">
         <v>329</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>296</v>
+      </c>
+      <c r="C85" t="n">
+        <v>165</v>
+      </c>
+      <c r="D85" t="n">
+        <v>31</v>
+      </c>
+      <c r="E85" t="n">
+        <v>20</v>
+      </c>
+      <c r="F85" t="n">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2045,26 @@
         <v>314</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n">
+        <v>335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2056,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3547,6 +3567,26 @@
       </c>
       <c r="F85" t="n">
         <v>245</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2065,28 @@
         <v>335</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>287</v>
+      </c>
+      <c r="C87" t="n">
+        <v>110</v>
+      </c>
+      <c r="D87" t="n">
+        <v>23</v>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2076,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3587,6 +3609,28 @@
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n">
         <v>195</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>598</v>
+      </c>
+      <c r="C87" t="n">
+        <v>99</v>
+      </c>
+      <c r="D87" t="n">
+        <v>18</v>
+      </c>
+      <c r="E87" t="n">
+        <v>12</v>
+      </c>
+      <c r="F87" t="n">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2087,6 +2087,28 @@
         <v>299</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2098,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3631,6 +3653,26 @@
       </c>
       <c r="F87" t="n">
         <v>414</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n">
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2109,6 +2109,16 @@
         <v>228</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2120,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3673,6 +3683,13 @@
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n">
         <v>381</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2119,6 +2119,22 @@
         <v>3</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2130,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3691,6 +3707,18 @@
           <t>2026-08-23</t>
         </is>
       </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2135,6 +2135,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>403</v>
+      </c>
+      <c r="C91" t="n">
+        <v>178</v>
+      </c>
+      <c r="D91" t="n">
+        <v>35</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="n">
+        <v>496</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2146,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3719,6 +3741,28 @@
       <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>618</v>
+      </c>
+      <c r="C91" t="n">
+        <v>140</v>
+      </c>
+      <c r="D91" t="n">
+        <v>38</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="n">
+        <v>367</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2157,28 @@
         <v>496</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>477</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2168,7 +2190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3762,6 +3784,26 @@
       </c>
       <c r="F91" t="n">
         <v>367</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n">
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2179,28 @@
         <v>428</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>293</v>
+      </c>
+      <c r="C93" t="n">
+        <v>99</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="n">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2190,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3804,6 +3826,25 @@
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n">
         <v>431</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>184</v>
+      </c>
+      <c r="C93" t="n">
+        <v>110</v>
+      </c>
+      <c r="D93" t="n">
+        <v>33</v>
+      </c>
+      <c r="F93" t="n">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2201,6 +2201,28 @@
         <v>287</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2212,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3845,6 +3867,24 @@
       </c>
       <c r="F93" t="n">
         <v>313</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2223,6 +2223,16 @@
         <v>62</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2234,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3885,6 +3895,13 @@
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2233,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2244,7 +2266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3902,6 +3924,26 @@
         <is>
           <t>2026-08-30</t>
         </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2255,28 @@
         <v>81</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>211</v>
+      </c>
+      <c r="C97" t="n">
+        <v>79</v>
+      </c>
+      <c r="D97" t="n">
+        <v>9</v>
+      </c>
+      <c r="E97" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" t="n">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2266,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3946,6 +3968,25 @@
         <v>182</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>341</v>
+      </c>
+      <c r="C97" t="n">
+        <v>111</v>
+      </c>
+      <c r="D97" t="n">
+        <v>24</v>
+      </c>
+      <c r="F97" t="n">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3957,7 +3998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5039,12 +5080,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1377708</t>
+          <t>1893384</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös, med pilar, WPH-01-A-xx</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -5056,12 +5097,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1377726</t>
+          <t>1893385</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös, med pilar, WPH-01-A-xx</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5073,12 +5114,12 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1377713</t>
+          <t>1893386</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-L</t>
+          <t>Tryckknapp trådlös, med pilar, WPH-01-A-xx</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -5090,12 +5131,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1377714</t>
+          <t>1893387</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-L</t>
+          <t>Tryckknapp trådlös, med pilar, WPH-01-A-xx</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5107,12 +5148,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1377773</t>
+          <t>1377708</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -5124,12 +5165,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1377772</t>
+          <t>1377726</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5141,12 +5182,12 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1377707</t>
+          <t>1377713</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -5158,12 +5199,12 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1377727</t>
+          <t>1377714</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5175,12 +5216,12 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1377737</t>
+          <t>1377773</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -5192,12 +5233,12 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1377735</t>
+          <t>1377772</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5209,12 +5250,12 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1377733</t>
+          <t>1377707</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -5226,12 +5267,12 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1377734</t>
+          <t>1377727</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -5243,12 +5284,12 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1377736</t>
+          <t>1377737</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -5260,15 +5301,83 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
+          <t>1377735</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>1377733</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>1377734</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>1377736</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
           <t>1377738</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2277,6 +2277,28 @@
         <v>232</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2288,7 +2310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3985,6 +4007,28 @@
       </c>
       <c r="F97" t="n">
         <v>315</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2299,6 +2299,28 @@
         <v>293</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>306</v>
+      </c>
+      <c r="C99" t="n">
+        <v>103</v>
+      </c>
+      <c r="D99" t="n">
+        <v>17</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2310,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4029,6 +4051,28 @@
       </c>
       <c r="F98" s="3" t="n">
         <v>215</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>128</v>
+      </c>
+      <c r="C99" t="n">
+        <v>79</v>
+      </c>
+      <c r="D99" t="n">
+        <v>13</v>
+      </c>
+      <c r="E99" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" t="n">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2321,6 +2321,26 @@
         <v>258</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="n">
+        <v>272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2332,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4073,6 +4093,28 @@
       </c>
       <c r="F99" t="n">
         <v>151</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2341,6 +2341,28 @@
         <v>272</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>228</v>
+      </c>
+      <c r="C101" t="n">
+        <v>99</v>
+      </c>
+      <c r="D101" t="n">
+        <v>13</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2352,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4115,6 +4137,25 @@
       </c>
       <c r="F100" s="3" t="n">
         <v>186</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>359</v>
+      </c>
+      <c r="C101" t="n">
+        <v>66</v>
+      </c>
+      <c r="D101" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" t="n">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2363,6 +2363,22 @@
         <v>251</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2374,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4157,6 +4173,18 @@
       <c r="F101" t="n">
         <v>299</v>
       </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2379,6 +2379,25 @@
         <v>4</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>33</v>
+      </c>
+      <c r="C103" t="n">
+        <v>18</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2390,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4185,6 +4204,25 @@
       <c r="D102" s="3" t="n"/>
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>211</v>
+      </c>
+      <c r="C103" t="n">
+        <v>49</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2398,6 +2398,26 @@
         <v>28</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2409,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4222,6 +4242,28 @@
       </c>
       <c r="F103" t="n">
         <v>89</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2418,6 +2418,28 @@
         <v>252</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>297</v>
+      </c>
+      <c r="C105" t="n">
+        <v>98</v>
+      </c>
+      <c r="D105" t="n">
+        <v>18</v>
+      </c>
+      <c r="E105" t="n">
+        <v>7</v>
+      </c>
+      <c r="F105" t="n">
+        <v>249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2429,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4264,6 +4286,25 @@
       </c>
       <c r="F104" s="3" t="n">
         <v>497</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>304</v>
+      </c>
+      <c r="C105" t="n">
+        <v>119</v>
+      </c>
+      <c r="D105" t="n">
+        <v>23</v>
+      </c>
+      <c r="F105" t="n">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2440,6 +2440,28 @@
         <v>249</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2451,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4305,6 +4327,26 @@
       </c>
       <c r="F105" t="n">
         <v>312</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2462,6 +2462,28 @@
         <v>266</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>342</v>
+      </c>
+      <c r="C107" t="n">
+        <v>105</v>
+      </c>
+      <c r="D107" t="n">
+        <v>15</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="n">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2473,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4347,6 +4369,28 @@
       <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="n">
         <v>118</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>78</v>
+      </c>
+      <c r="C107" t="n">
+        <v>115</v>
+      </c>
+      <c r="D107" t="n">
+        <v>12</v>
+      </c>
+      <c r="E107" t="n">
+        <v>8</v>
+      </c>
+      <c r="F107" t="n">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2484,6 +2484,28 @@
         <v>300</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>277</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2495,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4391,6 +4413,26 @@
       </c>
       <c r="F107" t="n">
         <v>184</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
